--- a/建設業許可申請チェックリスト_土木_修正版.xlsx
+++ b/建設業許可申請チェックリスト_土木_修正版.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="土木申請チェックリスト" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="優先度の見方" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="追加項目の根拠" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="根拠PDF一覧" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,34 +610,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>建設業許可申請 チェックリスト【土木のみ・第一段階】　沖縄県・法人・一般建設業（土木）新規　＜公式PDF照合・修正版 v2＞</t>
+          <t>建設業許可申請 チェックリスト【土木のみ・第一段階】　沖縄県・法人・一般建設業（土木）新規　＜公式PDF照合・修正版 v3：根拠列追加＞</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>提出3部（正・副・控）／A4フラットファイルに綴る／各証明書は発行後3ヶ月以内（残高証明書は1ヶ月以内）　※収入証紙：知事許可・新規・一般は通常9万円分（4.5万円は更新の金額の可能性）→面談予約時に必ず電話で要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>提出3部（正・副・控）／A4フラットファイルに綴る／各証明書は発行後3ヶ月以内（残高証明書は1ヶ月以内）　※「根拠」列の略号：【添付】=添付書類一覧R8.1.26版／【常勤】=常勤確認R7.6版／【経営】=過去の経営経験R3.6.17版</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
@@ -660,20 +661,25 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>根拠（PDF・該当箇所）</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>備考タグ</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>完了日</t>
         </is>
@@ -686,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>★1</t>
@@ -704,25 +710,30 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TEL: 098-866-2374　※書類提出前に予約必須。面談形式の審査あり。「土木のみ新規申請」と伝える。日程が決まれば全体スケジュールが組める</t>
+          <t>TEL: 098-866-2374　※書類提出前に予約必須。面談形式の審査あり。「土木のみ新規申請」と伝える</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
+          <t>沖縄県運用（PDF記載なし）。沖縄県HP「建設業許可」案内ページ</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
           <t>最初にやること</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>電話予約</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -731,7 +742,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>★2</t>
@@ -749,23 +760,28 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>年3件×6年分＝18件必要。建設工事の請負とわかるもの。社内書類の掘り起こしに時間がかかる</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+          <t>年3件×6年分＝18件必要（5年が要件のため余裕の6年分）。建設工事の請負とわかるもの。1件の建設工事で複数の請求書がある場合は1枚のみ添付可</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>【経営】(B)経験年数欄「建設工事の請負に関する契約書、請書、注文書、請求書等の写し（年３件分×証明期間年数分）」</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+      <c r="I7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>★2</t>
@@ -786,20 +802,25 @@
           <t>第15〜17号の2。直前決算期のもの。表紙の添付が必要。税理士への依頼が必要</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>【添付】第15号〜第17号の2「法」マーク欄。100分の5基準に緩和</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>自社（税理士）</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+      <c r="I8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>★2</t>
@@ -817,23 +838,28 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>証明期間分。該当ページ＋表紙をセットで提出</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="inlineStr">
+          <t>証明期間分。該当ページ＋表紙をセットで提出（許可番号変更なければ最初と最後の年のみ可）</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>【経営】(B)経験年数欄「東商企業要覧沖縄県版（写し）」「証明期間分の許可証明書（写し）」</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="42" customHeight="1">
+      <c r="I9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>★2</t>
@@ -851,25 +877,30 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>経管証明用＝(B)常勤確認。社長の証明期間（5〜6年分）の常勤がわかるもの。年金事務所窓口で「被保険者記録照会回答票」を本人請求。発行に時間がかかるため早めに着手</t>
+          <t>経管証明用＝(B)常勤確認。社長の証明期間（5〜6年分）の常勤がわかるもの。年金事務所窓口で本人請求。発行に時間がかかるため早めに着手</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
+          <t>【経営】常勤確認書類（証明期間）欄「被保険者記録照会回答票などの写しを提出（申請業者において証明期間、常勤であったことを確認できるもの）」</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
           <t>発行後3ヶ月以内</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>年金事務所</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -878,7 +909,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>★3</t>
@@ -901,22 +932,27 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
+          <t>【経営】(A)経験年数欄「履歴事項全部証明書（原本）又は閉鎖登記簿謄本（原本）」</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
           <t>原本提出</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>法務局</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="I12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>★3</t>
@@ -939,22 +975,27 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
+          <t>【添付】「登記事項証明書（商業登記簿）」法マーク・原本提出</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
           <t>原本提出</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>法務局</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+      <c r="I13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>★3</t>
@@ -977,22 +1018,27 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
+          <t>【添付】「後見等登記事項証明書」◎「法人：役員、建設業法施行令第3条に規定する使用人」</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
           <t>原本提出</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>法務局</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+      <c r="I14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>★3</t>
@@ -1015,22 +1061,27 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
+          <t>【添付】「常勤の役員等（経営業務の管理責任者）、常勤の役員等及び直接補佐する者の住民票」◎</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
           <t>原本提示＋写し</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>市区町村</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+      <c r="I15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>★3</t>
@@ -1053,22 +1104,27 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
+          <t>【添付】「身分証明書（本籍地の役所で取得可能）」◎「法人：別紙1に記載した役員等全員」原本提出</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
           <t>原本提出</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>本籍地役所</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+      <c r="I16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>★3</t>
@@ -1091,22 +1147,27 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
+          <t>【添付】「営業所技術者の住民票」◎</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
           <t>原本提示＋写し</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>市区町村</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>上原</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+      <c r="I17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>★3</t>
@@ -1129,20 +1190,25 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
+          <t>【添付】「納税証明書（法人事業税又は個人事業税）」◎原本提出。県税、直前1期分</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
           <t>原本提出</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>県税事務所</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1151,7 +1217,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1172,20 +1238,25 @@
           <t>沖縄県HPからDL。提出時に該当項目にマーカーまたはチェックを入れて提出</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「沖縄県様式 【新規申請用】チェックシート」◎</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
+      <c r="I20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1206,20 +1277,25 @@
           <t>沖縄県HPからDL・作成</t>
         </is>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「沖縄県様式 表紙（建設業許可申請書）」◎／「第1号 建設業許可申請書」◎</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
+      <c r="I21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1240,20 +1316,25 @@
           <t>営業所の写真（外観・入口・内部）を添付。令和5年12月から必須</t>
         </is>
       </c>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「別紙二(1) 営業所一覧表（新規許可等）」◎＋「第20号 営業の沿革」◎。営業所新設の場合は写真添付の注記あり</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>県HP＋自社撮影</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
+      <c r="I22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1274,20 +1355,25 @@
           <t>実績の有無に関わらず必要。工事実績確認できる契約書等の提示が必要</t>
         </is>
       </c>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第2号 工事経歴書」◎</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24" ht="28" customHeight="1">
+      <c r="I23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1308,20 +1394,25 @@
           <t>実績の有無に関わらず必要</t>
         </is>
       </c>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第3号 直前3年の各事業年度における工事施工金額」◎</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
+      <c r="I24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1342,20 +1433,25 @@
           <t>沖縄県HPからDL・作成</t>
         </is>
       </c>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第4号 使用人数」◎</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
+      <c r="I25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1376,20 +1472,25 @@
           <t>本文の削除不可。申請者名は代表者名を記入</t>
         </is>
       </c>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第6号 誓約書」◎「本文の削除はしない」</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="42" customHeight="1">
+      <c r="I26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1407,23 +1508,28 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>沖縄県HPからDL・作成。証明内容の確認書類（写し）を添付（★2の被保険者記録照会回答票・履歴事項全部証明書・契約書18件・東商要覧）</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="inlineStr">
+          <t>県HPからDL・作成。証明内容の確認書類（写し）を添付（★2の被保険者記録照会回答票・履歴事項全部証明書・契約書18件・東商要覧）</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第7号 常勤役員等（経営業務の管理責任者等）証明書」○＋「別紙 常勤役員等の略歴書」○</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
+      <c r="I27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1444,20 +1550,25 @@
           <t>健保・厚生年金：直前の保険料領収証書または納入証明書の写し／雇用保険：労働保険概算・確定保険料申告書の控え＋領収済通知書の写し</t>
         </is>
       </c>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第7号の3 健康保険等の加入状況」◎。添付書類の詳細記載あり</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>県HP＋会社</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
+      <c r="I28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1478,20 +1589,25 @@
           <t>土木担当分（上原）を作成</t>
         </is>
       </c>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「別紙四 営業所技術者一覧表」◎＋「第8号 営業所技術者証明書（新規・変更）」◎</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
+      <c r="I29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1512,20 +1628,25 @@
           <t>役員＋相談役・顧問・5%以上出資者も記載（今回は社長1名のみ）</t>
         </is>
       </c>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「別紙一 役員等の一覧表」◎「100分の5以上に相当する出資をしている者も記載」</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" ht="28" customHeight="1">
+      <c r="I30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1546,20 +1667,25 @@
           <t>役員等全員分（今回は社長1名のみ）</t>
         </is>
       </c>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第12号 許可申請者等の住所、生年月日等に関する調書」◎「法人：別紙1に記載した役員等全員」</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="28" customHeight="1">
+      <c r="I31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1580,20 +1706,25 @@
           <t>法人は必須。沖縄県HPからDLし、出資者全員分を記載</t>
         </is>
       </c>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第14号 株主（出資者）調書」法マーク＝法人申請者は必須</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="28" customHeight="1">
+      <c r="I32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1614,20 +1745,25 @@
           <t>沖縄県HPからDL・作成</t>
         </is>
       </c>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第20号の2 所属建設業者団体」◎</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="28" customHeight="1">
+      <c r="I33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
           <t>★4</t>
@@ -1648,18 +1784,23 @@
           <t>沖縄県HPからDL・作成</t>
         </is>
       </c>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>【添付】「第20号の3 主要取引金融機関名」◎</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>県HP</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -1668,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
+    <row r="36" ht="36" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
           <t>★5</t>
@@ -1691,22 +1832,27 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
+          <t>【添付】「営業所技術者としての資格を有することを証明する資料」◎「資格証明書（写し添付＋原本持参）」</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
           <t>写し添付＋原本持参</t>
         </is>
       </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>自己保管</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>上原</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr"/>
-    </row>
-    <row r="37" ht="42" customHeight="1">
+      <c r="I36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
           <t>★5</t>
@@ -1724,27 +1870,32 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>健保・厚生年金被保険者標準報酬決定通知書の写し、または資格取得届（確認印あり）等。報酬が最低賃金を下回ると常勤不可（法人役員は除く）</t>
+          <t>健保・厚生年金被保険者標準報酬決定通知書の写し、または資格取得届（確認印あり）等。報酬が最低賃金を下回ると常勤不可（法人役員は除外）</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
+          <t>【常勤】2.社会保険（健康保険）が確認できる書類（1）ア〜エのいずれか【提示】</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
           <t>原本提示</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>会社</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="H37" s="13" t="inlineStr"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
+      <c r="I37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
           <t>★5</t>
@@ -1762,27 +1913,32 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>健保・厚生年金被保険者標準報酬決定通知書等。原本提示。報酬が最低賃金を下回ると常勤として認められない</t>
+          <t>健保・厚生年金被保険者標準報酬決定通知書等。原本提示</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
+          <t>【常勤】2.社会保険（健康保険）が確認できる書類（1）ア〜エのいずれか【提示】</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
           <t>原本提示</t>
         </is>
       </c>
-      <c r="F38" s="13" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>会社</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="H38" s="13" t="inlineStr"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
+      <c r="I38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
           <t>★5</t>
@@ -1803,20 +1959,25 @@
           <t>自社保管のもの</t>
         </is>
       </c>
-      <c r="E39" s="13" t="n"/>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>【添付】「定款」法マーク</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H39" s="13" t="inlineStr"/>
-    </row>
-    <row r="40" ht="28" customHeight="1">
+      <c r="I39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
           <t>★5</t>
@@ -1839,20 +2000,25 @@
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
+          <t>【添付】「法人番号指定通知書」法マーク「法人番号がわかる画面コピーでも可」</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
           <t>写しでOK</t>
         </is>
       </c>
-      <c r="F40" s="13" t="inlineStr">
+      <c r="G40" s="13" t="inlineStr">
         <is>
           <t>自社／国税庁HP</t>
         </is>
       </c>
-      <c r="G40" s="13" t="inlineStr">
+      <c r="H40" s="13" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="H40" s="13" t="inlineStr"/>
+      <c r="I40" s="13" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -1861,7 +2027,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
+    <row r="42" ht="40" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
           <t>★6</t>
@@ -1884,22 +2050,27 @@
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
+          <t>【添付】「財産的要件を確認する資料」○一般建設業：預金残高証明書（500万円以上。証明日が申請日前1ヶ月以内。原本提示）</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
           <t>申請直前1ヶ月以内・原本提示</t>
         </is>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>取引銀行</t>
         </is>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="H42" s="15" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr"/>
-    </row>
-    <row r="43" ht="56" customHeight="1">
+      <c r="I42" s="15" t="inlineStr"/>
+    </row>
+    <row r="43" ht="52" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
           <t>★6</t>
@@ -1922,20 +2093,25 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
+          <t>【添付】「別紙三 収入印紙、証紙等貼付欄」◎「沖縄県証紙」。金額は沖縄県HP「建設業許可手数料」</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
           <t>★要電話確認</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="G43" s="15" t="inlineStr">
         <is>
           <t>郵便局等</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H43" s="15" t="inlineStr"/>
+      <c r="I43" s="15" t="inlineStr"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -1944,7 +2120,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
+    <row r="45" ht="36" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>予定</t>
@@ -1967,22 +2143,27 @@
       </c>
       <c r="E45" s="17" t="inlineStr">
         <is>
+          <t>（業種追加時の営業所技術者要件）</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
           <t>合格後</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="G45" s="17" t="inlineStr">
         <is>
           <t>試験機関</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
+      <c r="H45" s="17" t="inlineStr">
         <is>
           <t>本人</t>
         </is>
       </c>
-      <c r="H45" s="17" t="inlineStr"/>
-    </row>
-    <row r="46" ht="28" customHeight="1">
+      <c r="I45" s="17" t="inlineStr"/>
+    </row>
+    <row r="46" ht="36" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>予定</t>
@@ -2005,20 +2186,25 @@
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
+          <t>【添付】業種追加欄（◎/○/△マーク）参照</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
           <t>合格後</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="G46" s="17" t="inlineStr">
         <is>
           <t>沖縄県</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="H46" s="17" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="H46" s="17" t="inlineStr"/>
+      <c r="I46" s="17" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
@@ -2065,108 +2251,116 @@
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>■追加①（★4・黄マーカー）：第14号 株主（出資者）調書 — 法人は必須</t>
+          <t>■v3変更：本体シートに「根拠（PDF・該当箇所）」列を追加。略号【添付】【常勤】【経営】でPDFを参照</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>■追加②（★5・黄マーカー）：法人番号指定通知書 写し — 法人は必須（国税庁HP画面コピー可）</t>
+          <t>■追加①（★4・黄マーカー）：第14号 株主（出資者）調書 — 法人は必須</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>■追加③（★2・黄マーカー）：過去の常勤確認書類＝被保険者記録照会回答票 — 経管証明の(B)常勤確認用／年金事務所</t>
+          <t>■追加②（★5・黄マーカー）：法人番号指定通知書 写し — 法人は必須（国税庁HP画面コピー可）</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="21" t="inlineStr">
         <is>
-          <t>■修正①：収入証紙金額「4.5万円」→「要電話確認」へ（知事許可・新規・一般は通常9万円。4.5万円は更新の金額の可能性）</t>
+          <t>■追加③（★2・黄マーカー）：過去の常勤確認書類＝被保険者記録照会回答票 — 経管証明の(B)常勤確認用／年金事務所</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>■補足①：書類順を最新版PDF（R8.1.26）の「許可申請書及び添付書類一覧」の並び順に整列</t>
+          <t>■修正①：収入証紙金額「4.5万円」→「要電話確認」へ（知事許可・新規・一般は通常9万円。4.5万円は更新の金額の可能性）</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="21" t="inlineStr">
         <is>
-          <t>■補足②：健康保険等の加入状況（第7号の3）はP5→P4に移動（県HPからDLする様式のため）</t>
+          <t>■補足①：書類順を最新版PDF（R8.1.26）の「許可申請書及び添付書類一覧」の並び順に整列</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="21" t="inlineStr">
         <is>
-          <t>■確認済：役員＝社長1名のみ → 後見等登記/身分証明書/第12号調書は社長分のみでOK</t>
+          <t>■補足②：健康保険等の加入状況（第7号の3）はP5→P4に移動（県HPからDLする様式のため）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="21" t="inlineStr">
         <is>
-          <t>■確認済：上原氏＝従業員（非役員・非令3条使用人）→ 後見/身分/第11号一覧表/第13号調書は不要、住民票＋常勤確認のみ</t>
+          <t>■確認済：役員＝社長1名のみ → 後見等登記/身分証明書/第12号調書は社長分のみでOK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="21" t="inlineStr">
         <is>
-          <t>■確認済：過去の経営経験は自社で5年以上 → 履歴事項全部証明書＋契約書18件＋東商企業要覧＋(B)被保険者記録照会回答票</t>
+          <t>■確認済：上原氏＝従業員（非役員・非令3条使用人）→ 後見/身分/第11号一覧表/第13号調書は不要、住民票＋常勤確認のみ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>■参考：附属明細表（第17号の3）は資本金1億円超 or 直前BS負債200億円以上の株式会社のみ必須（該当なければ不要）</t>
+          <t>■確認済：過去の経営経験は自社で5年以上 → 履歴事項全部証明書＋契約書18件＋東商企業要覧＋(B)被保険者記録照会回答票</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="21" t="inlineStr">
         <is>
+          <t>■参考：附属明細表（第17号の3）は資本金1億円超 or 直前BS負債200億円以上の株式会社のみ必須（該当なければ不要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="inlineStr">
+        <is>
           <t>■参考：事業承継チェックシート（jigyoushoukei.pdf）は譲渡・合併・分割・相続用のため、新規取得では不要</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A58:H58"/>
+  <mergeCells count="27">
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2333,94 +2527,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>略号</t>
         </is>
       </c>
       <c r="B1" s="22" t="inlineStr">
         <is>
-          <t>根拠（公式PDFの該当箇所）</t>
+          <t>PDFファイル名</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>第14号 株主（出資者）調書</t>
+          <t>【添付】</t>
         </is>
       </c>
       <c r="B2" s="29" t="inlineStr">
         <is>
-          <t>tenpushoruiichiran_20260126.pdf：第14号 株主（出資者）調書 — 「法」マーク＝法人申請者は必須</t>
+          <t>checksheet_tenpushoruiichiran_20260126.pdf</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>沖縄県版「許可申請書及び添付書類一覧」（R8.1.26＝2026.1.26最新版）。新規・更新・業種追加すべての必要書類を◎○△で示した一覧表</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="29" t="inlineStr">
         <is>
-          <t>法人番号指定通知書</t>
+          <t>【常勤】</t>
         </is>
       </c>
       <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>tenpushoruiichiran_20260126.pdf：法人番号指定通知書 — 「法」マーク＝法人必須。「法人番号がわかる画面コピーでも可」</t>
+          <t>checksheet_jyokinkakunin_20250618.pdf</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>常勤確認の書類（R7.6現在）。経管・営業所技術者・令3条使用人・支配人の現時点での常勤を証明する書類の詳細</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>過去の常勤確認書類（被保険者記録照会回答票）</t>
+          <t>【経営】</t>
         </is>
       </c>
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>kakonokeieikeiken_20210617.pdf：常勤確認書類（証明期間）欄 — 「被保険者記録照会回答票などの写しを提出（申請業者において証明期間、常勤であったことを確認できるもの）」</t>
+          <t>checksheet_kakonokeieikeiken_20210617.pdf</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>常勤役員等の過去の経営経験の確認資料（R3.6.17修正）。(A)経験年数・(B)経験内容・常勤確認の3点セットを規定</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>収入証紙の金額確認</t>
+          <t>（参考）</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>公式PDFに金額の直接記載はないため、面談予約電話（098-866-2374）で必ず確認。沖縄県知事許可・新規・一般は一般的に9万円（県収入証紙）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>社長分のみでOK（後見/身分/第12号）</t>
-        </is>
-      </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>tenpushoruiichiran_20260126.pdf：後見等登記事項証明書「法人：役員、令第3条使用人」／身分証明書「法人：別紙1に記載した役員等全員」／第12号「法人：別紙1に記載した役員等全員」 → 役員＝社長1名のため社長分のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>上原氏（営業所技術者）の書類</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>tenpushoruiichiran_20260126.pdf：営業所技術者は住民票（◎）＋資格証明書＋常勤確認のみ。後見/身分/第11号/第13号は令第3条使用人（支店長等）のみ必要</t>
+          <t>checksheet_jigyoushoukei.pdf</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>事業承継用（譲渡・合併・分割・相続）チェックシート。新規取得では使わない</t>
         </is>
       </c>
     </row>

--- a/建設業許可申請チェックリスト_土木_修正版.xlsx
+++ b/建設業許可申請チェックリスト_土木_修正版.xlsx
@@ -10,6 +10,7 @@
     <sheet name="土木申請チェックリスト" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="優先度の見方" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="根拠PDF一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="公共工事ロードマップ" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +69,24 @@
     <font>
       <name val="Yu Gothic"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="14">
@@ -138,7 +157,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,11 +179,55 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -244,6 +307,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,7 +711,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>建設業許可申請 チェックリスト【土木のみ・第一段階】　沖縄県・法人・一般建設業（土木）新規　＜公式PDF照合・修正版 v3：根拠列追加＞</t>
+          <t>建設業許可申請 チェックリスト【土木のみ・第一段階】　沖縄県・法人・一般建設業（土木）新規　＜公式PDF照合・修正版 v4：公共工事ロードマップ追加＞</t>
         </is>
       </c>
     </row>
@@ -2623,4 +2707,513 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>公共工事参入ロードマップ（建設業許可取得後の流れ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>建設業許可（今回）→ 決算変更届 → 経営状況分析 → 経営事項審査（経審）→ 入札参加資格申請 → 公共工事入札参加</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ステップ</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>費用</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>申請先</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>建設業許可取得</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>今回</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>知事許可・一般建設業（土木）・新規申請。本チェックリストv3の通り</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>収入証紙9万円（要確認）</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>決算変更届</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>毎期決算後4ヶ月以内</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>事業年度終了後4ヶ月以内に毎年提出。工事経歴書・直前3年の工事施工金額・財務諸表・納税証明書等。経審を受ける年は、ここで決算変更届を完了させてから経審申請</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>0円（自社作成）</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>経営状況分析</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>経審の1〜2ヶ月前</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>民間の「登録経営状況分析機関」へ依頼（全国10社程度。例：(一財)建設業情報管理センター、(株)経営状況分析センター等）。Y点（経営状況評点）が算出される</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>1〜2万円程度（機関による）</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>登録分析機関</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>経営事項審査（経審）</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>毎年（有効期限1年7ヶ月）</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Y点（経営状況）＋X1（完成工事高）＋X2（自己資本・利益額）＋Z（技術職員・元請完工高）＋W（社会性・社会保険等）を総合してP点（総合評定値）を算出。工事経歴書・財務諸表・技術職員名簿・社会保険加入証明等が必要</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>11,000円＋業種数×2,500円</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>入札参加資格審査申請</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>各発注機関の定期受付</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>P点を元に各発注機関がA・B・C・Dランク（または1〜4等級）に格付け。沖縄県・那覇市・沖縄総合事務局など、参加したい発注機関ごとに別途申請。定期受付は2年に1回（沖縄県は1月頃、年度によって異なる）。期間外は随時受付の機関もあり</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>0円〜（機関による）</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>県・市町村・国</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>公共工事入札参加</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>ランク確定後</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>ランクに応じた金額帯の工事に入札可能。例：Aランク=高額工事、Dランク=小規模工事</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>各発注機関</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>★今の建設業許可申請時から意識すると、後の経審が楽になるポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>工事経歴書（第2号）の作り方を経審ベースに</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>経審では「土木一式の元請完成工事高」が業種別に集計される。許可申請時から元請/下請・業種を正確に分類しておくと、経審時の遡及修正が不要になる</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>社会保険・雇用保険にしっかり加入</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>経審W点（社会性）の最重要項目。健康保険・厚生年金・雇用保険の3つ全加入で加点。未加入の保険があると大幅減点。許可申請の第7号の3で証明する加入状況がそのまま経審にも使われる</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>技術職員を増やす計画</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>経審Z点は「技術職員数×資格区分の点数」。1級・2級施工管理技士、技術士、監理技術者証等が高得点。上原氏の2級土木に加え、今後1級取得を目指すと評点が大幅アップ</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>自己資本の積み上げ</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>経審X2点に直結。一般建設業の財産要件は500万円だが、経審では自己資本が大きいほど高得点。新規申請時の500万円残高証明はあくまで最低ライン。事業継続中に内部留保を増やす意識を</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>健康診断・退職金共済等の加入</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>経審W点の加点項目：①建設業退職金共済（建退共）、②中小企業退職金共済、③法定外労災保険、④雇用や賃金水準、⑤建設機械保有、⑥ISO9001/14001、⑦防災協定締結 等</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>決算月の選択</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>経審の有効期限は審査基準日（決算日）から1年7ヶ月。決算月＝経審申請のタイミングを決めるので、入札参加機関の定期受付スケジュールと合わせると効率的</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>CCUS（建設キャリアアップシステム）登録</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>経審W点の加点項目（R5.1〜）。事業者登録＋技能者登録で加点。沖縄県内でも公共工事では実質必須化の流れ</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n"/>
+      <c r="F19" s="35" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>★沖縄県の主要発注機関・入札参加資格申請の窓口</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>発注機関</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="35" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>土木建築部 技術・建設業課（経審）／総務部 管財課（入札参加資格）。定期受付は2年に1回。県HP「建設工事入札参加資格審査申請」で告知</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="35" t="n"/>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>那覇市</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>総務部 契約検査課。定期受付は2年に1回。市HPで告知</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>沖縄総合事務局（国土交通省）</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>国の発注工事。沖縄県内では国道・港湾・空港等。「競争参加資格審査申請（建設工事）」を国へ提出。受付は定期＋随時</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="35" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>その他市町村</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>市町村ごとに独自の入札参加資格審査制度。沖縄市・うるま市・宜野湾市・浦添市等、進出したい地域の自治体HPを確認</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="n"/>
+      <c r="D26" s="34" t="n"/>
+      <c r="E26" s="34" t="n"/>
+      <c r="F26" s="35" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>※経審・入札参加資格の手続きは建設業許可とは別制度。本チェックリストv3の許可取得が完了した後、公共工事に参入したいタイミングで上記ステップ2〜5を順番に進める。なお民間工事のみであればこれらの手続きは一切不要</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B13:F13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/建設業許可申請チェックリスト_土木_修正版.xlsx
+++ b/建設業許可申請チェックリスト_土木_修正版.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="土木申請チェックリスト" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="優先度の見方" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="根拠PDF一覧" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="公共工事ロードマップ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="経管5年の積み上げ確認" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="優先度の見方" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="根拠PDF一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="公共工事ロードマップ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,8 +89,20 @@
       <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +167,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -227,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -327,6 +345,33 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -694,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -711,7 +756,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>建設業許可申請 チェックリスト【土木のみ・第一段階】　沖縄県・法人・一般建設業（土木）新規　＜公式PDF照合・修正版 v4：公共工事ロードマップ追加＞</t>
+          <t>建設業許可申請 チェックリスト【土木のみ・第一段階】　沖縄県・法人・一般建設業（土木）新規　＜公式PDF照合・修正版 v5：経管5年の積み上げ＝前職役員経験の合算を反映＞</t>
         </is>
       </c>
     </row>
@@ -844,7 +889,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>年3件×6年分＝18件必要（5年が要件のため余裕の6年分）。建設工事の請負とわかるもの。1件の建設工事で複数の請求書がある場合は1枚のみ添付可</t>
+          <t>経管証明用。年3件×証明年数分。⚠自社の工事実績はR5年〜の約3年分のみ＝5年に不足。不足分は社長の前職（他の建設会社の役員）経験を合算して5年を満たす。前職が許可業者なら許可証明書で代替可、無許可なら前職会社の工事契約書(年3件×在籍年数)が必要。1件で複数請求書がある場合は1枚のみ添付可。詳細は別シート「経管5年の積み上げ確認」参照</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -2398,7 +2443,7 @@
     <row r="64">
       <c r="A64" s="21" t="inlineStr">
         <is>
-          <t>■確認済：過去の経営経験は自社で5年以上 → 履歴事項全部証明書＋契約書18件＋東商企業要覧＋(B)被保険者記録照会回答票</t>
+          <t>■要確認【最重要】：経管5年は自社実績(R5〜約3年)だけでは不足。社長の前職(他の建設会社の役員)経験を合算して5年に到達させる方針。①前職の役員在籍期間(履歴事項/閉鎖事項証明書で確認)②前職の許可有無 を要確認。別シート参照</t>
         </is>
       </c>
     </row>
@@ -2416,8 +2461,22 @@
         </is>
       </c>
     </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="21" t="inlineStr">
+        <is>
+          <t>■v5変更【最重要】：経管5年の前提を修正。会社設立R3でも工事実績はR5〜のため自社では約3年分のみ＝5年に不足。社長の前職(他の建設会社の役員)経験を合算して5年を満たす方針に変更。★2契約書欄・確認済欄を更新し、別シート「経管5年の積み上げ確認」を新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>■v5確認事項：①前職での役員在籍期間（前の会社の履歴事項全部証明書／閉鎖事項証明書で確定。登記は公開情報のため誰でも取得可）②前職在籍時の建設業許可の有無（許可業者なら許可証明書の写しで証明が容易）③被保険者記録照会回答票で前職の在籍・常勤も裏付け可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="29">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A66:I66"/>
@@ -2432,7 +2491,9 @@
     <mergeCell ref="A52:I52"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A67:I67"/>
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="A48:I48"/>
     <mergeCell ref="A64:I64"/>
@@ -2456,6 +2517,556 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>経管（経営業務の管理責任者等）5年の積み上げ確認　【申請可否を左右する最重要前提】</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>区分：建設業法施行規則 第7条 第1号 イ(1)「建設業に関し5年以上 経営業務の管理責任者としての経験を有する者」（1人体制＝様式第7号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>■ 問題点：会社が5年目でも、自社の工事実績だけでは5年に足りない</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>経管の「5年」は実際に建設業を営んでいた期間のみカウント。証明は『年3件×証明年数分の工事契約書類』。自社は工事の請負がR5年からのため、約3年分しか証明できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>■ 期間カウント表（現状）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>年(和暦/西暦)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>立場</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>カウント</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>証明書類</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>設立前 (〜R3)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>前の建設会社の役員</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>★ここを合算する（在籍期間を要確認）</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>○ 合算可</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>前職の履歴事項/閉鎖事項証明書＋許可証明書or工事契約書</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>R3 / 2021</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="inlineStr">
+        <is>
+          <t>自社設立</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>工事実績なし？（要確認）</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>△ 実績あれば</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>R3の工事契約書類があれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>R4 / 2022</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>工事実績なし？（要確認）</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>△ 実績あれば</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>R4の工事契約書類があれば</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>R5 / 2023</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>自社・役員</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>工事請負 開始</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>工事契約書類 年3件</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>R6 / 2024</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>自社・役員</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>工事あり</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>工事契約書類 年3件</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>R7 / 2025</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>自社・役員</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>工事あり</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>工事契約書類 年3件</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>R8 / 2026 (現在)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>自社・役員</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>工事あり（期中）</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>工事契約書類</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>→ 自社分(R5〜)＝約3年。前職の役員期間が2年以上あれば合算で5年到達の見込み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>■ 前職（他の建設会社の役員）を合算するための必要書類</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>確認事項</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>必要書類</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>入手先</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>役員在籍期間</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>前の会社の履歴事項全部証明書（原本）／退任が古い場合は閉鎖事項証明書も</t>
+        </is>
+      </c>
+      <c r="D20" s="37" t="inlineStr">
+        <is>
+          <t>法務局（登記は公開情報。誰でも取得可）</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>□ 要取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>建設業だった証明</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>いずれか</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>①許可業者だった場合：許可証明書（写し）※一番ラク</t>
+        </is>
+      </c>
+      <c r="D21" s="37" t="inlineStr">
+        <is>
+          <t>前の会社／許可行政庁</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>□ 要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>建設業だった証明</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>いずれか</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>②無許可の場合：工事契約書・請書・注文書・請求書（年3件×在籍年数分）</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>前の会社（協力が必要）</t>
+        </is>
+      </c>
+      <c r="E22" s="44" t="inlineStr">
+        <is>
+          <t>□ 要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>当時の常勤性</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>補強</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>被保険者記録照会回答票（前職の健保加入歴＝在籍・常勤の裏付け）</t>
+        </is>
+      </c>
+      <c r="D23" s="37" t="inlineStr">
+        <is>
+          <t>年金事務所（社長本人）</t>
+        </is>
+      </c>
+      <c r="E23" s="44" t="inlineStr">
+        <is>
+          <t>□ v3で追加済</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>■ 判定フロー（確認結果でこう動く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="46" t="inlineStr">
+        <is>
+          <t>【前職の役員期間は？】</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>├ 2年以上 → 自社R5〜の約3年と合算で【5年達成】✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>│    ├ 前職が許可業者 → 許可証明書（写し）で簡単に証明【ラク】</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="46" t="inlineStr">
+        <is>
+          <t>│    └ 前職が無許可 → 前の会社の工事契約書類(年3件×在籍年数)が必要 ※相手会社の協力が要る</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="46" t="inlineStr">
+        <is>
+          <t>├ 1〜2年 → 合算で約4〜5年（ギリギリ）。R3・R4の自社工事実績も拾えれば確実</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="46" t="inlineStr">
+        <is>
+          <t>└ 1年未満／前職が使えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       ├ R3・R4に自社で工事をしていた証拠（無許可の軽微工事でも可）を探す</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └ それも無ければ【5年到達まで待機】(R5起点で概ねR10/2028頃)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>■ メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="47" t="inlineStr">
+        <is>
+          <t>・経管5年は1社で連続している必要はなく、複数の会社・期間を通算できる（他社の取締役経験も合算可）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="47" t="inlineStr">
+        <is>
+          <t>・他社の役員(取締役)経験は、イ(1)の「経営業務の管理責任者としての経験」に直接該当する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="47" t="inlineStr">
+        <is>
+          <t>・建設業許可がない時期の軽微な工事（500万円未満）でも、建設業の経営経験としてカウントされる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="47" t="inlineStr">
+        <is>
+          <t>・前の会社の登記事項証明書は公開情報。商号と本店所在地（会社法人番号があれば確実）がわかれば、自社でなくても取得できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="47" t="inlineStr">
+        <is>
+          <t>・最終判断は沖縄県 技術・建設業課との面談（★1）で必ず確認すること。合算可否・必要書類の運用は窓口確認が確実。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A40:E40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2605,7 +3216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2709,7 +3320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
